--- a/YouTube이슈분석_개인채널_2026-08-01.xlsx
+++ b/YouTube이슈분석_개인채널_2026-08-01.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>날짜</t>
   </si>
@@ -95,10 +95,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>1974년생 채준석 교수는 고려대를 졸업 후 미국 미시간대에서 박사 학위를 취득하고 애리조나 주립대 부교수로 재직하던 중, 2020년 3월 실종되었습니다. 이후 사건 수사를 통해 범죄 사실이 드러났으며, 영상은 실종부터 수사, 체포, 재판 과정에 이르기까지 해당 사건의 전말을 다루고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목으로 시청자를 유도하는 범죄 사건 요약 콘텐츠이므로, 사실 관계 확인 시 정식 언론 보도를 병행하여 확인하는 것이 좋습니다.</t>
+    <t>1974년생 채준석 교수는 고려대를 졸업 후 미국 미시간대에서 박사 학위를 취득하고 애리조나 주립대 교수로 재직했습니다. 하지만 2020년 3월 퇴근 후 실종되었고, 이후 시신으로 발견되는 안타까운 범죄 사건에 휘말렸습니다. 본 영상은 채 교수의 실종 배경부터 수사 과정, 가해자의 주장 및 재판 결과까지 사건의 전말을 상세히 다루고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 실제 범죄 사건을 다루고 있으므로 다소 충격적인 내용이 포함될 수 있으니 시청 시 유의하시기 바랍니다.</t>
   </si>
   <si>
     <t>▶</t>
@@ -122,46 +122,43 @@
     <t>14:50</t>
   </si>
   <si>
-    <t>본 영상은 헤노코 매립 공사 관련 해상 사고와 그에 따른 형사 고소 사건이 축소되고 있다는 의혹을 다룹니다. 스다 신이치로는 이 사건의 배경에 있는 교육 기관과 운항 단체의 책임 소재를 지적하며, 이것이 타마키 데니 오키나와 지사의 선거 결과 및 정치적 이해관계와 어떤 연결고리를 갖는지 심층적으로 분석하고 의문을 제기합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 특정 정치적 의혹을 제기하는 논평 성격이 강하므로, 정보의 사실관계 확인을 위해 관련 언론 보도와 공식 수사 발표를 함께 교차 검증하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【事件解説】羽賀研二さん含む7人が逮捕された事件　その中には山口組弘道会傘下組長も？ についてお話します</t>
-  </si>
-  <si>
-    <t>シン・懲役太郎チャンネル</t>
+    <t>본 영상은 헤노코 매립지 인근에서 발생한 선박 전복 사고와 관련하여, 학교와 운항 단체를 대상으로 한 형사 고소가 의도적으로 축소되고 있을 가능성을 제기합니다. 스다 신이치로는 이번 사건의 배경에 다마키 데니 오키나와 지사의 선거 캠페인 및 정치적 이해관계가 얽혀 있을 수 있음을 지적하며, 관련 의혹에 대한 심도 있는 분석과 주의를 촉구하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️정치적 이슈를 다루는 영상의 경우 특정 개인이나 단체를 겨냥한 주장이 포함될 수 있으므로, 보도된 사실관계와 정치적 견해를 분리하여 객관적으로 확인하는 태도가 필요합니다.</t>
+  </si>
+  <si>
+    <t>速度だけを追い求め時間旅行を叶えた超音速旅客機「コンコルド」【事件事故】</t>
+  </si>
+  <si>
+    <t>奇妙な夜</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>초음속 여객기 '콩코드'의 탄생과 역사, 그리고 그 이면에 숨겨진 사건과 사고를 다룬 영상입니다. 단순한 이동 수단을 넘어 인류의 기술적 도전을 상징했던 콩코드가 왜 역사 속으로 사라지게 되었는지, 그 화려했던 비행과 비극적인 결말을 조명하며 항공 역사상 가장 혁신적이었던 기체의 흥망성쇠를 심도 있게 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 미스터리한 분위기를 강조하지만, 실제 내용은 콩코드의 기술적 성과와 퇴역 과정을 다룬 항공 역사 다큐멘터리에 가깝습니다.</t>
+  </si>
+  <si>
+    <t>【衝撃の結末と事件の全貌】京都南丹市小5男児事件</t>
+  </si>
+  <si>
+    <t>話題の事件</t>
   </si>
   <si>
     <t>2026-07-31</t>
   </si>
   <si>
-    <t>13:27</t>
-  </si>
-  <si>
-    <t>본 영상은 연예인 하가 켄지가 포함된 7명이 체포된 사건을 다룹니다. 특히 체포 인원 중 야쿠자 조직인 야마구치구미 산하 고도카이 계열의 조장이 포함되어 있다는 의혹을 중심으로, 사건의 배경과 조직 간의 관계성을 법적·사회적 관점에서 상세히 분석하여 설명하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 연예인 사건과 조직 폭력배의 연루설을 다루는 자극적인 소재이므로, 사실관계 확인 시 출처를 반드시 교차 검증해야 합니다.</t>
-  </si>
-  <si>
-    <t>【ノリで強盗致傷】18歳専門学生2人の末路…少年院か少年刑務所か【かなえ先生の切り抜き】元配信2026/07/23</t>
-  </si>
-  <si>
-    <t>【公認】かなえ先生への共感【Vtuber】</t>
-  </si>
-  <si>
-    <t>2026-07-25</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>본 영상은 18세 전문학교 학생 2명이 충동적으로 저지른 강도치상 사건을 다룹니다. 카나에 선생님이 해당 사건의 심각성을 범죄학적 관점에서 분석하며, 소년법의 적용 범위와 소년원 및 소년교도소의 차이점, 수감 생활의 실태를 상세히 설명하여 청소년 범죄의 경각심을 일깨웁니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 범죄 뉴스에 현혹되기보다 법적 처벌 체계와 사건의 본질적 원인을 파악하는 비판적 시각이 필요합니다.</t>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>본 영상은 교토 난탄시에서 발생한 초등학교 5학년 남아 실종 및 사망 사건의 전말을 다룹니다. 혈연관계가 없는 의붓아버지와의 복잡한 가정 환경 속에서 비극적인 결말을 맞이하게 된 사건의 경위를 분석하며, 사건의 교훈과 범죄 예방의 중요성을 강조합니다. 채널은 실제 사건을 바탕으로 정보 전달 및 방범 의식 고취를 목적으로 제작되었으며, AI 생성 이미지 등을 활용해 사건의 실체를 재구성하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 자극적인 소재를 다루는 만큼 시청 시 주의가 필요하며, 제공되는 정보가 실제 사건을 바탕으로 재구성된 교육적 목적의 콘텐츠임을 인지하고 시청하시기 바랍니다.</t>
   </si>
   <si>
     <t>미국</t>
@@ -182,25 +179,10 @@
     <t>11:38</t>
   </si>
   <si>
-    <t>유튜버 'The Anime Man(Joey)'이 틱톡에서 여성 주인공 애니메이션을 추천했다가 트위터 사용자들로부터 큰 반발을 산 사건을 다룹니다. Rev says desu 채널은 이 상황의 심각성과 커뮤니티 내의 갈등을 분석하며, 특정 콘텐츠에 대한 대중의 반응과 그로 인한 온라인 논란을 집중적으로 조명하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 유튜브의 자극적인 제목과 썸네일은 논란을 부각해 조회수를 유도하는 클릭베이트일 가능성이 높으니 실제 내용을 비판적으로 수용하세요.</t>
-  </si>
-  <si>
-    <t>Jantar Mantar ka Sabse Viral Moment 🔥 | Politics Xpose</t>
-  </si>
-  <si>
-    <t>Politics Xpose</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>이 영상은 잔타르 만타르에서 한 청년이 모디 총리와 인도 국민당(BJP)을 강도 높게 비판하며 화제가 된 순간을 다룹니다. 해당 발언은 소셜 미디어에서 뜨거운 논쟁과 수많은 밈을 생성하며 바이럴되었습니다. 영상은 정치적 사건을 로스트와 풍자, 엔터테인먼트적 관점으로 재구성하여 시청자들에게 정치 상황을 비판적이고 흥미로운 시각으로 전달하는 데 초점을 맞추고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 이 영상은 자극적인 정치 풍자와 로스트 형식을 띠고 있으므로 객관적인 정보보다는 특정 관점이 강조된 엔터테인먼트 콘텐츠로 시청하는 것이 좋습니다.</t>
+    <t>유튜버 Rev says desu가 '애니메 맨(The Anime Man)' 조이의 최근 논란을 다룹니다. 조이가 틱톡에서 여성 주인공 애니메이션을 추천했다가 트위터에서 강한 반발을 산 상황을 설명하며, 온라인 커뮤니티의 과열된 반응과 비판적 여론 형성 과정을 분석하는 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 썸네일을 사용하는 논란 중심의 채널이므로, 정보 습득 시 객관적인 사실관계 확인이 필요합니다.</t>
   </si>
   <si>
     <t>BREAKING: Cleaned-Up SINKING BOAT Call Reveals What Many Missed in Nolan Wells Case</t>
@@ -212,10 +194,10 @@
     <t>16:05</t>
   </si>
   <si>
-    <t>윌리 D 라이브 채널은 놀란 웰스 사건의 보트 침몰 당시 녹음된 오디오를 오디오 엔지니어 자넷 브랜틀리가 정밀 분석하여 법 집행 기관이 놓친 배경 음성을 새롭게 발견했다고 주장합니다. 이 분석은 미시시피 보트 미스터리 사건의 진상을 뒤흔들 수 있는 결정적인 증거를 제시하며, 기존의 AI 기술이 아닌 전통적인 스튜디오 기법을 통해 배경 소음을 분리하여 사건의 숨겨진 단서를 밝혀내고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 제목과 썸네일을 활용한 클릭베이트 성격이 강하므로 객관적인 정보 확인을 위해 신중한 시청이 필요합니다.</t>
+    <t>Willie D Live는 놀란 웰스 사건의 침몰 보트 통화 오디오를 음향 엔지니어 지네타 브랜틀리가 정밀 분석한 결과를 다룹니다. 기존 소프트웨어 방식이 아닌 전통적인 스튜디오 기술로 배경 소음을 제거하여 법 집행 기관이 간과했던 새로운 음성 증거를 포착했으며, 이것이 미시시피 보트 사건의 진실을 뒤흔들 중요한 단서가 될 수 있다고 주장합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 시청자를 유도하는 전형적인 트루 크라임 분석 영상이므로, 제공된 정보의 객관성을 비판적으로 검토할 필요가 있습니다.</t>
   </si>
   <si>
     <t>Afşin Hatipoğlu'ndan Kritik Gürsel Tekin İddiası! 'Genel Başkan Adayı Olmak için Hazırlıklara...'</t>
@@ -230,91 +212,73 @@
     <t>10:29</t>
   </si>
   <si>
-    <t>Sözcü TV'nin bu yayınında, CHP İstanbul İl Başkanlığı'ndaki kapı kırma olayı, parti içi arınma tartışmaları ve Sarıyer'deki 'cast ajansı' soruşturması ele alınıyor. Hukukçu Afşin Hatipoğlu, siyasi gelişmeleri hukuki perspektifle değerlendirirken, Kemal Kılıçdaroğlu yönetimine yönelik eleştiriler ve Gürsel Tekin'in genel başkan adaylığı iddiası gibi kritik parti gündemleri detaylandırılıyor.</t>
-  </si>
-  <si>
-    <t>⚠️ Videonun başlığı Gürsel Tekin'in adaylık iddiasına odaklansa da, içeriğin büyük bir kısmı parti içi tartışmalar ve hukuki süreçlerden oluştuğu için beklentiyi bu yönde tutmanız faydalı olacaktır.</t>
+    <t>Sözcü TV'de CHP içindeki güncel krizler masaya yatırıldı. Afşin Hatipoğlu, İstanbul İl Başkanlığı'ndaki kapı kırma olayı, parti içi 'arınma' tartışmaları ve Sarıyer'deki 'cast ajansı' soruşturmasını hukuki ve siyasi açılardan değerlendirdi. Programda ayrıca Kemal Kılıçdaroğlu yönetimine yönelik eleştiriler ile Gürsel Tekin'in genel başkan adaylığı iddiaları gündeme taşındı.</t>
+  </si>
+  <si>
+    <t>⚠️ Videonun başlığında yer alan iddialar, siyasi kulis söylentilerine dayanan dikkat çekici içeriklerdir, bu yüzden izlerken resmi açıklamalarla kıyaslama yapmanız önerilir.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t>【大谷翔平】14度目の敬遠で本拠地大ブーイングにレジェンドが衝撃本音【海外の反応 MLBメジャー 野球】</t>
-  </si>
-  <si>
-    <t>今日の大谷速報</t>
-  </si>
-  <si>
-    <t>2026-07-30</t>
-  </si>
-  <si>
-    <t>20:49</t>
-  </si>
-  <si>
-    <t>이 영상은 메이저리그에서 오타니 쇼헤이 선수가 상대 팀으로부터 14번째 고의사구(경원)를 당했을 때, 홈 팬들이 보인 격렬한 야유와 이에 대한 야구계 레전드들의 솔직한 반응을 다루고 있습니다. 오타니를 향한 집중 견제 상황과 그를 둘러싼 현지의 뜨거운 여론을 깊이 있게 분석하며, MLB 경기에서 벌어지는 전략적 승부와 팬들의 심리를 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 썸네일과 제목을 사용하여 클릭을 유도하는 경향이 있으므로, 선수에 대한 과장된 반응보다는 실제 경기 기록과 공식 인터뷰를 병행하여 확인하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【2026/07/30】がーどまん   【ガチ説教】那須川天心と炎上してるガミックスを合わせたら試合決定しました。twitch録画保管庫</t>
-  </si>
-  <si>
-    <t>がーどまんtwitch録画保管庫</t>
-  </si>
-  <si>
-    <t>1:04:25</t>
-  </si>
-  <si>
-    <t>가드맨(Gardman)의 트위치 방송 영상으로, 격투기 선수 나스카와 텐신과 논란의 중심에 있는 가믹스를 대면시켜 긴장감 넘치는 상황을 연출합니다. 영상은 가드맨 특유의 거친 설교와 도발이 섞인 분위기 속에서 두 인물의 만남을 성사시키며, 단순한 대화를 넘어 실제 경기 매치업이 성사되는 과정을 다룹니다. 자극적인 화법을 통해 시청자들의 관심을 끄는 전형적인 가드맨식 콘텐츠를 담고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 갈등 연출과 과장된 언행이 포함된 영상이므로 실제 상황보다는 예능적 재미로 시청하는 것을 권장합니다.</t>
-  </si>
-  <si>
-    <t>[海外の反応] 韓国「日本が頭を下げるなら手を貸してやる」アセアンを見下した提案→10カ国の答えに絶句...</t>
-  </si>
-  <si>
-    <t>SMOKINGxKUSH</t>
-  </si>
-  <si>
-    <t>52:02</t>
-  </si>
-  <si>
-    <t>이 영상은 특정 국가 간의 외교적 갈등이나 태도를 다루는 해외 반응형 콘텐츠로, 한국의 제안에 대한 아세안 국가들의 반응을 다루는 자극적인 제목을 사용하고 있습니다. 하지만 실제 영상 내용은 채널 소개와 감동적인 인간 드라마를 강조하는 일반적인 안내 멘트로 구성되어 있어, 제목의 정치적 이슈와는 무관한 낚시성 콘텐츠임을 알 수 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 채널의 영상들은 자극적인 제목과 실제 내용이 일치하지 않는 클릭베이트 형식이 많으므로 시청 시 주의가 필요합니다.</t>
-  </si>
-  <si>
-    <t>"Trump's Own Party Just HUMILIATED Him in the Worst Way!" | Bill Clinton</t>
-  </si>
-  <si>
-    <t>Regalado Regalado</t>
-  </si>
-  <si>
-    <t>20:14</t>
-  </si>
-  <si>
-    <t>빌 클린턴 전 대통령이 상원 사법위원회에서 벌어진 트럼프 행정부 법무장관 지명자 인준 지연 사태를 분석합니다. 공화당 상원의원들이 자당 지명자의 인준을 반대하며 트럼프에게 정치적 타격을 준 상황을 설명하며, 이것이 미국 민주주의와 정부 운영에 어떤 의미를 갖는지 비판적 시각에서 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 제목에서 강력한 정치적 갈등을 강조하고 있으므로, 사실 확인을 위해 주요 외신 보도와 교차 검증하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【緊急】杉尾秀哉さん、被災地へ向かう自衛隊を邪魔した件で謝罪するも更に大炎上.....</t>
-  </si>
-  <si>
-    <t>【速報】国民の本音まるわかり党</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>본 영상은 입헌민주당 스기오 히데야 의원이 과거 재해 현장으로 향하던 자위대 차량을 방해했다는 논란에 대해 사과했음에도 불구하고, 대중의 거센 비판과 함께 더욱 큰 논란으로 번진 상황을 다룹니다. 채널은 이를 정치적 이슈로 부각하며 국민의 시각에서 비판적으로 분석하는 콘텐츠를 제공합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 채널은 정치적 성향이 강하고 자극적인 편집을 사용하는 가십성 정치 채널이므로, 영상 속 정보를 수용할 때 교차 검증이 필요합니다.</t>
+    <t>TIKTOK MASHUP VIRAL AUGUST 2026 PHILIPPINES</t>
+  </si>
+  <si>
+    <t>Mayumi Tiktok Mashup</t>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>이 영상은 2026년 8월 필리핀 지역에서 유행한 틱톡의 인기 댄스 챌린지와 바이럴 영상들을 하나로 편집한 매시업 콘텐츠입니다. 시청자들이 트렌디한 영상들을 한눈에 즐길 수 있도록 제작되었으며, 빠른 비트와 함께 화제가 된 밈과 스킷들이 포함되어 있어 최신 소셜 미디어 흐름을 파악하기에 적합합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 이 영상은 자극적인 썸네일과 클릭베이트 형식을 사용하고 있으므로, 기대치를 낮추고 가벼운 오락용으로만 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【海外の反応】「5兆円払え」韓国大統領の衝撃発言に日本が沈黙→3ヶ月後、韓国を襲った＂予想外の代償＂に世界が絶句</t>
+  </si>
+  <si>
+    <t>世界が憧れる 京都の美</t>
+  </si>
+  <si>
+    <t>25:33</t>
+  </si>
+  <si>
+    <t>본 영상은 한국 대통령의 일본을 향한 강경한 발언과 그에 따른 한일 관계의 급변을 다루는 자극적인 정치적 소재의 영상입니다. 표면적으로는 한국의 요구와 그로 인한 대가에 대해 다루지만, 실제 내용은 전형적인 유튜브 클릭베이트(낚시성) 콘텐츠의 형식을 띄고 있으며, 감정적인 대립과 충격적인 결말을 강조하여 시청자의 조회수를 유도하는 구성입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 썸네일을 활용하여 조회수를 유도하는 클릭베이트성 영상이므로, 구체적인 사실관계는 반드시 신뢰할 수 있는 언론 매체를 통해 직접 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>TIKTOK MASHUP VIRAL July 2026 PHILIPPINES</t>
+  </si>
+  <si>
+    <t>Loramashup</t>
+  </si>
+  <si>
+    <t>10:31</t>
+  </si>
+  <si>
+    <t>이 영상은 필리핀 지역에서 2026년 7월 기준으로 유행하는 틱톡의 인기 댄스 챌린지, 밈, 그리고 화제의 영상들을 하나로 편집한 매쉬업 콘텐츠입니다. 시청자들에게 최신 트렌드와 흥미로운 순간들을 빠르게 전달하며, 채널 구독과 알림 설정을 통해 지속적인 업데이트를 제공하겠다는 홍보성 메시지를 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 유행을 앞세운 전형적인 클릭베이트 영상이므로, 실제 필리핀의 최신 문화 트렌드를 파악하는 용도로만 참고하세요.</t>
+  </si>
+  <si>
+    <t>8月1日 プロ野球ニュース #118 🅵🆄🅻🅻🆂🅷🅾🆆</t>
+  </si>
+  <si>
+    <t>Lợi La ứ Team Hoàng Em 14</t>
+  </si>
+  <si>
+    <t>53:04</t>
+  </si>
+  <si>
+    <t>8월 1일 일본 프로야구 뉴스 #118은 당일 치러진 경기 결과와 주요 하이라이트를 종합적으로 정리한 영상입니다. 요미우리 자이언츠, 한신 타이거즈, 오릭스 버팔로스 등 NPB 12개 구단의 경기 내용과 선수들의 활약상을 상세히 전달하며 리그 순위 변동과 주요 이슈를 다룹니다.</t>
+  </si>
+  <si>
+    <t>일본 프로야구의 실시간 경기 결과와 각 팀의 전력 현황을 빠르게 파악하고 싶은 팬들에게 유용한 요약 영상입니다.</t>
   </si>
 </sst>
 </file>
@@ -701,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -786,16 +750,16 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>27352</v>
+        <v>33760</v>
       </c>
       <c r="J2" s="3">
-        <v>510</v>
+        <v>592</v>
       </c>
       <c r="K2" s="3">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="L2" s="3">
-        <v>4608</v>
+        <v>4950</v>
       </c>
       <c r="M2" s="3">
         <v>165000</v>
@@ -842,19 +806,19 @@
         <v>34</v>
       </c>
       <c r="I3" s="3">
-        <v>146557</v>
+        <v>147719</v>
       </c>
       <c r="J3" s="3">
-        <v>7506</v>
+        <v>7567</v>
       </c>
       <c r="K3" s="3">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="L3" s="3">
-        <v>40059</v>
+        <v>34709</v>
       </c>
       <c r="M3" s="3">
-        <v>163000</v>
+        <v>164000</v>
       </c>
       <c r="N3" s="5">
         <v>0.9</v>
@@ -892,34 +856,34 @@
         <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="I4" s="3">
-        <v>34642</v>
+        <v>47803</v>
       </c>
       <c r="J4" s="3">
-        <v>435</v>
+        <v>652</v>
       </c>
       <c r="K4" s="3">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="L4" s="3">
-        <v>10350</v>
+        <v>17983</v>
       </c>
       <c r="M4" s="3">
-        <v>52300</v>
+        <v>144000</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>25</v>
       </c>
       <c r="O4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>28</v>
@@ -942,40 +906,40 @@
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="I5" s="3">
-        <v>28428</v>
+        <v>48521</v>
       </c>
       <c r="J5" s="3">
-        <v>509</v>
+        <v>1241</v>
       </c>
       <c r="K5" s="3">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3">
-        <v>3708</v>
+        <v>14107</v>
       </c>
       <c r="M5" s="3">
-        <v>174000</v>
+        <v>189000</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="O5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>28</v>
@@ -989,49 +953,49 @@
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="I6" s="3">
-        <v>122000</v>
+        <v>124168</v>
       </c>
       <c r="J6" s="3">
-        <v>6218</v>
+        <v>6315</v>
       </c>
       <c r="K6" s="3">
-        <v>2716</v>
+        <v>2744</v>
       </c>
       <c r="L6" s="3">
-        <v>60830</v>
+        <v>53453</v>
       </c>
       <c r="M6" s="3">
         <v>752000</v>
       </c>
       <c r="N6" s="5">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="O6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>28</v>
@@ -1045,49 +1009,49 @@
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="3">
+        <v>123241</v>
+      </c>
+      <c r="J7" s="3">
+        <v>9018</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2536</v>
+      </c>
+      <c r="L7" s="3">
+        <v>49667</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="3">
-        <v>33227</v>
-      </c>
-      <c r="J7" s="3">
-        <v>428</v>
-      </c>
-      <c r="K7" s="3">
-        <v>23</v>
-      </c>
-      <c r="L7" s="3">
-        <v>3432</v>
-      </c>
-      <c r="M7" s="3">
-        <v>3620</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>28</v>
@@ -1101,43 +1065,43 @@
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I8" s="3">
-        <v>122857</v>
+        <v>37622</v>
       </c>
       <c r="J8" s="3">
-        <v>9005</v>
+        <v>730</v>
       </c>
       <c r="K8" s="3">
-        <v>2470</v>
+        <v>72</v>
       </c>
       <c r="L8" s="3">
-        <v>54469</v>
+        <v>4883</v>
       </c>
       <c r="M8" s="3">
-        <v>1180000</v>
-      </c>
-      <c r="N8" s="5">
-        <v>0.1</v>
+        <v>2300000</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>65</v>
@@ -1149,62 +1113,6 @@
         <v>28</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="3">
-        <v>37264</v>
-      </c>
-      <c r="J9" s="3">
-        <v>724</v>
-      </c>
-      <c r="K9" s="3">
-        <v>70</v>
-      </c>
-      <c r="L9" s="3">
-        <v>5272</v>
-      </c>
-      <c r="M9" s="3">
-        <v>2300000</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R9" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1217,7 +1125,6 @@
     <hyperlink ref="Q6" r:id="rId5"/>
     <hyperlink ref="Q7" r:id="rId6"/>
     <hyperlink ref="Q8" r:id="rId7"/>
-    <hyperlink ref="Q9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1225,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1289,49 +1196,49 @@
         <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="I2" s="3">
-        <v>113365</v>
+        <v>67267</v>
       </c>
       <c r="J2" s="3">
-        <v>342</v>
+        <v>156</v>
       </c>
       <c r="K2" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>181</v>
+        <v>442</v>
       </c>
       <c r="N2" s="5">
-        <v>626</v>
+        <v>152</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>28</v>
@@ -1348,46 +1255,46 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I3" s="3">
-        <v>100669</v>
+        <v>89791</v>
       </c>
       <c r="J3" s="3">
-        <v>1069</v>
+        <v>703</v>
       </c>
       <c r="K3" s="3">
-        <v>513</v>
+        <v>122</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>610</v>
+        <v>882</v>
       </c>
       <c r="N3" s="5">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>28</v>
@@ -1401,49 +1308,49 @@
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I4" s="3">
-        <v>72923</v>
+        <v>119557</v>
       </c>
       <c r="J4" s="3">
-        <v>797</v>
+        <v>206</v>
       </c>
       <c r="K4" s="3">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>1110</v>
+        <v>1420</v>
       </c>
       <c r="N4" s="5">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>28</v>
@@ -1457,110 +1364,54 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I5" s="3">
-        <v>51660</v>
+        <v>59220</v>
       </c>
       <c r="J5" s="3">
-        <v>1489</v>
+        <v>511</v>
       </c>
       <c r="K5" s="3">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>2930</v>
+        <v>3690</v>
       </c>
       <c r="N5" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="3">
-        <v>56622</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1202</v>
-      </c>
-      <c r="K6" s="3">
-        <v>257</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>3580</v>
-      </c>
-      <c r="N6" s="5">
-        <v>16</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1570,7 +1421,6 @@
     <hyperlink ref="Q3" r:id="rId2"/>
     <hyperlink ref="Q4" r:id="rId3"/>
     <hyperlink ref="Q5" r:id="rId4"/>
-    <hyperlink ref="Q6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
